--- a/펫호텔/ex2_요구사항지시서_회사양식.xlsx
+++ b/펫호텔/ex2_요구사항지시서_회사양식.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imchaeil/Documents/git/pethotel/펫호텔/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cof99\Documents\git\pethotel\펫호텔\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B10306C-55BD-CB45-AEDD-ABD0758BF202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11FF6D5-E5A9-44DA-B416-040C710C858A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17780" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="-12840" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="요구사항개요" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3467" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3507" uniqueCount="741">
   <si>
     <t>문서명</t>
   </si>
@@ -2272,6 +2272,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2288,6 +2289,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> (</t>
     </r>
@@ -2304,6 +2306,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -2323,6 +2326,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2339,6 +2343,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2355,6 +2360,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2371,6 +2377,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2387,6 +2394,10 @@
   </si>
   <si>
     <t>필수값 누락 시 진행 불가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3162,14 +3173,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3177,7 +3188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3185,7 +3196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -3193,7 +3204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -3201,7 +3212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16">
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -3209,7 +3220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -3217,12 +3228,15 @@
         <v>193</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="I8" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -3234,7 +3248,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -3246,7 +3260,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3254,7 +3268,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -3262,7 +3276,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -3270,7 +3284,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -3278,7 +3292,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3286,7 +3300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -3315,7 +3329,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>178</v>
       </c>
@@ -3341,10 +3355,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>182</v>
       </c>
@@ -3370,10 +3384,10 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>184</v>
       </c>
@@ -3399,10 +3413,10 @@
         <v>87</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>186</v>
       </c>
@@ -3428,10 +3442,10 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>188</v>
       </c>
@@ -3457,10 +3471,10 @@
         <v>87</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>190</v>
       </c>
@@ -3486,10 +3500,10 @@
         <v>87</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>193</v>
       </c>
@@ -3515,10 +3529,10 @@
         <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>195</v>
       </c>
@@ -3544,10 +3558,10 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>198</v>
       </c>
@@ -3573,10 +3587,10 @@
         <v>87</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28.8">
       <c r="A17" s="2" t="s">
         <v>201</v>
       </c>
@@ -3602,10 +3616,10 @@
         <v>87</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>203</v>
       </c>
@@ -3631,7 +3645,7 @@
         <v>87</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -3657,7 +3671,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:I38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -3669,7 +3683,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3677,7 +3691,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -3685,7 +3699,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -3693,7 +3707,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -3701,7 +3715,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3709,7 +3723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -3738,7 +3752,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>205</v>
       </c>
@@ -3764,10 +3778,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>440</v>
       </c>
@@ -3793,10 +3807,10 @@
         <v>395</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>442</v>
       </c>
@@ -3822,10 +3836,10 @@
         <v>395</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>210</v>
       </c>
@@ -3851,10 +3865,10 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>444</v>
       </c>
@@ -3880,10 +3894,10 @@
         <v>395</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>446</v>
       </c>
@@ -3909,10 +3923,10 @@
         <v>395</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>448</v>
       </c>
@@ -3938,10 +3952,10 @@
         <v>395</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>450</v>
       </c>
@@ -3967,10 +3981,10 @@
         <v>395</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>213</v>
       </c>
@@ -3996,10 +4010,10 @@
         <v>87</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>215</v>
       </c>
@@ -4025,10 +4039,10 @@
         <v>87</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>217</v>
       </c>
@@ -4054,10 +4068,10 @@
         <v>87</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>219</v>
       </c>
@@ -4083,10 +4097,10 @@
         <v>87</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
         <v>452</v>
       </c>
@@ -4112,10 +4126,10 @@
         <v>395</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
         <v>222</v>
       </c>
@@ -4141,10 +4155,10 @@
         <v>87</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
         <v>454</v>
       </c>
@@ -4170,10 +4184,10 @@
         <v>395</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
         <v>224</v>
       </c>
@@ -4199,10 +4213,10 @@
         <v>87</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
         <v>226</v>
       </c>
@@ -4228,10 +4242,10 @@
         <v>87</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
         <v>456</v>
       </c>
@@ -4257,10 +4271,10 @@
         <v>395</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
         <v>229</v>
       </c>
@@ -4286,10 +4300,10 @@
         <v>87</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
         <v>458</v>
       </c>
@@ -4315,10 +4329,10 @@
         <v>395</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
         <v>460</v>
       </c>
@@ -4344,10 +4358,10 @@
         <v>395</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
         <v>462</v>
       </c>
@@ -4373,10 +4387,10 @@
         <v>395</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
         <v>464</v>
       </c>
@@ -4402,10 +4416,10 @@
         <v>395</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
         <v>466</v>
       </c>
@@ -4431,10 +4445,10 @@
         <v>395</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
         <v>468</v>
       </c>
@@ -4460,10 +4474,10 @@
         <v>395</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
         <v>470</v>
       </c>
@@ -4489,10 +4503,10 @@
         <v>395</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
         <v>472</v>
       </c>
@@ -4518,10 +4532,10 @@
         <v>395</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
         <v>474</v>
       </c>
@@ -4547,10 +4561,10 @@
         <v>395</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
         <v>475</v>
       </c>
@@ -4576,10 +4590,10 @@
         <v>395</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="28.8">
       <c r="A37" s="2" t="s">
         <v>230</v>
       </c>
@@ -4605,10 +4619,10 @@
         <v>87</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="28.8">
       <c r="A38" s="2" t="s">
         <v>233</v>
       </c>
@@ -4634,7 +4648,7 @@
         <v>87</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -4660,7 +4674,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -4672,7 +4686,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4680,7 +4694,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -4688,7 +4702,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -4696,7 +4710,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -4704,7 +4718,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -4712,7 +4726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -4741,7 +4755,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>477</v>
       </c>
@@ -4767,10 +4781,10 @@
         <v>395</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>480</v>
       </c>
@@ -4796,10 +4810,10 @@
         <v>395</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>482</v>
       </c>
@@ -4825,10 +4839,10 @@
         <v>395</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>484</v>
       </c>
@@ -4854,10 +4868,10 @@
         <v>395</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>486</v>
       </c>
@@ -4883,10 +4897,10 @@
         <v>395</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>488</v>
       </c>
@@ -4912,10 +4926,10 @@
         <v>395</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -4941,10 +4955,10 @@
         <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>239</v>
       </c>
@@ -4970,10 +4984,10 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>490</v>
       </c>
@@ -4999,10 +5013,10 @@
         <v>395</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>492</v>
       </c>
@@ -5028,10 +5042,10 @@
         <v>395</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>494</v>
       </c>
@@ -5057,10 +5071,10 @@
         <v>395</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>496</v>
       </c>
@@ -5086,10 +5100,10 @@
         <v>395</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
         <v>241</v>
       </c>
@@ -5115,10 +5129,10 @@
         <v>87</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
         <v>244</v>
       </c>
@@ -5144,10 +5158,10 @@
         <v>87</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
         <v>498</v>
       </c>
@@ -5173,10 +5187,10 @@
         <v>395</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
         <v>500</v>
       </c>
@@ -5202,10 +5216,10 @@
         <v>395</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
         <v>502</v>
       </c>
@@ -5231,10 +5245,10 @@
         <v>395</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
         <v>504</v>
       </c>
@@ -5260,10 +5274,10 @@
         <v>395</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
         <v>506</v>
       </c>
@@ -5289,10 +5303,10 @@
         <v>395</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
         <v>246</v>
       </c>
@@ -5318,10 +5332,10 @@
         <v>87</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
         <v>247</v>
       </c>
@@ -5347,7 +5361,7 @@
         <v>87</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -5373,7 +5387,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -5385,7 +5399,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5393,7 +5407,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -5401,7 +5415,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -5409,7 +5423,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -5417,7 +5431,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -5425,7 +5439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -5454,7 +5468,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>249</v>
       </c>
@@ -5480,10 +5494,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>253</v>
       </c>
@@ -5509,10 +5523,10 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>255</v>
       </c>
@@ -5538,10 +5552,10 @@
         <v>87</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>256</v>
       </c>
@@ -5567,10 +5581,10 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>258</v>
       </c>
@@ -5596,7 +5610,7 @@
         <v>87</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -5622,7 +5636,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -5634,7 +5648,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5642,7 +5656,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -5650,7 +5664,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -5658,7 +5672,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -5666,7 +5680,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -5674,7 +5688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -5703,7 +5717,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>260</v>
       </c>
@@ -5729,10 +5743,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>264</v>
       </c>
@@ -5758,10 +5772,10 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>508</v>
       </c>
@@ -5787,10 +5801,10 @@
         <v>395</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>266</v>
       </c>
@@ -5816,10 +5830,10 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>510</v>
       </c>
@@ -5845,10 +5859,10 @@
         <v>395</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>512</v>
       </c>
@@ -5874,10 +5888,10 @@
         <v>395</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>514</v>
       </c>
@@ -5903,7 +5917,7 @@
         <v>395</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -5929,7 +5943,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -5941,7 +5955,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5949,7 +5963,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9" ht="28.8">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -5957,7 +5971,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -5965,7 +5979,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -5973,7 +5987,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -5981,7 +5995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -6010,7 +6024,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9" ht="28.8">
       <c r="A8" s="2" t="s">
         <v>516</v>
       </c>
@@ -6036,10 +6050,10 @@
         <v>395</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>518</v>
       </c>
@@ -6065,7 +6079,7 @@
         <v>395</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -6091,7 +6105,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:I36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -6103,7 +6117,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6111,7 +6125,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="32">
+    <row r="2" spans="1:9" ht="28.8">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -6119,7 +6133,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -6127,7 +6141,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -6135,7 +6149,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -6143,7 +6157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -6172,7 +6186,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="32">
+    <row r="8" spans="1:9" ht="28.8">
       <c r="A8" s="2" t="s">
         <v>520</v>
       </c>
@@ -6198,10 +6212,10 @@
         <v>395</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>522</v>
       </c>
@@ -6227,10 +6241,10 @@
         <v>395</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.8">
       <c r="A10" s="2" t="s">
         <v>524</v>
       </c>
@@ -6256,10 +6270,10 @@
         <v>395</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>526</v>
       </c>
@@ -6285,10 +6299,10 @@
         <v>395</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>268</v>
       </c>
@@ -6314,10 +6328,10 @@
         <v>87</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28.8">
       <c r="A13" s="2" t="s">
         <v>527</v>
       </c>
@@ -6343,10 +6357,10 @@
         <v>395</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>271</v>
       </c>
@@ -6372,10 +6386,10 @@
         <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="28.8">
       <c r="A15" s="2" t="s">
         <v>273</v>
       </c>
@@ -6401,10 +6415,10 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="28.8">
       <c r="A16" s="2" t="s">
         <v>275</v>
       </c>
@@ -6430,10 +6444,10 @@
         <v>87</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28.8">
       <c r="A17" s="2" t="s">
         <v>277</v>
       </c>
@@ -6459,10 +6473,10 @@
         <v>87</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28.8">
       <c r="A18" s="2" t="s">
         <v>528</v>
       </c>
@@ -6488,10 +6502,10 @@
         <v>395</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="28.8">
       <c r="A19" s="2" t="s">
         <v>530</v>
       </c>
@@ -6517,10 +6531,10 @@
         <v>395</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.8">
       <c r="A20" s="2" t="s">
         <v>279</v>
       </c>
@@ -6546,10 +6560,10 @@
         <v>87</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28.8">
       <c r="A21" s="2" t="s">
         <v>532</v>
       </c>
@@ -6575,10 +6589,10 @@
         <v>395</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="28.8">
       <c r="A22" s="2" t="s">
         <v>534</v>
       </c>
@@ -6604,10 +6618,10 @@
         <v>395</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28.8">
       <c r="A23" s="2" t="s">
         <v>282</v>
       </c>
@@ -6633,10 +6647,10 @@
         <v>87</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="28.8">
       <c r="A24" s="2" t="s">
         <v>284</v>
       </c>
@@ -6662,10 +6676,10 @@
         <v>87</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="28.8">
       <c r="A25" s="2" t="s">
         <v>536</v>
       </c>
@@ -6691,10 +6705,10 @@
         <v>395</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="28.8">
       <c r="A26" s="2" t="s">
         <v>538</v>
       </c>
@@ -6720,10 +6734,10 @@
         <v>395</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.8">
       <c r="A27" s="2" t="s">
         <v>540</v>
       </c>
@@ -6749,10 +6763,10 @@
         <v>395</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="28.8">
       <c r="A28" s="2" t="s">
         <v>542</v>
       </c>
@@ -6778,10 +6792,10 @@
         <v>395</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="28.8">
       <c r="A29" s="2" t="s">
         <v>544</v>
       </c>
@@ -6807,10 +6821,10 @@
         <v>395</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="28.8">
       <c r="A30" s="2" t="s">
         <v>546</v>
       </c>
@@ -6836,10 +6850,10 @@
         <v>395</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="28.8">
       <c r="A31" s="2" t="s">
         <v>286</v>
       </c>
@@ -6865,10 +6879,10 @@
         <v>87</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="28.8">
       <c r="A32" s="2" t="s">
         <v>289</v>
       </c>
@@ -6894,10 +6908,10 @@
         <v>87</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="28.8">
       <c r="A33" s="2" t="s">
         <v>291</v>
       </c>
@@ -6923,10 +6937,10 @@
         <v>87</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="28.8">
       <c r="A34" s="2" t="s">
         <v>294</v>
       </c>
@@ -6952,10 +6966,10 @@
         <v>87</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="28.8">
       <c r="A35" s="2" t="s">
         <v>296</v>
       </c>
@@ -6981,10 +6995,10 @@
         <v>87</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="28.8">
       <c r="A36" s="2" t="s">
         <v>298</v>
       </c>
@@ -7010,7 +7024,7 @@
         <v>87</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -7036,7 +7050,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -7048,7 +7062,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7056,7 +7070,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="32">
+    <row r="2" spans="1:9" ht="28.8">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -7064,7 +7078,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -7072,7 +7086,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -7080,7 +7094,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -7088,7 +7102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -7117,7 +7131,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="32">
+    <row r="8" spans="1:9" ht="28.8">
       <c r="A8" s="2" t="s">
         <v>301</v>
       </c>
@@ -7143,10 +7157,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>305</v>
       </c>
@@ -7172,10 +7186,10 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.8">
       <c r="A10" s="2" t="s">
         <v>307</v>
       </c>
@@ -7201,10 +7215,10 @@
         <v>87</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>308</v>
       </c>
@@ -7230,7 +7244,7 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -7256,7 +7270,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -7268,7 +7282,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7276,7 +7290,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9" ht="28.8">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -7284,7 +7298,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -7292,7 +7306,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -7300,7 +7314,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -7308,7 +7322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -7337,7 +7351,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9" ht="28.8">
       <c r="A8" s="2" t="s">
         <v>548</v>
       </c>
@@ -7363,10 +7377,10 @@
         <v>395</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.8">
       <c r="A9" s="2" t="s">
         <v>550</v>
       </c>
@@ -7392,10 +7406,10 @@
         <v>395</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.8">
       <c r="A10" s="2" t="s">
         <v>552</v>
       </c>
@@ -7421,10 +7435,10 @@
         <v>395</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.8">
       <c r="A11" s="2" t="s">
         <v>554</v>
       </c>
@@ -7450,10 +7464,10 @@
         <v>395</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>556</v>
       </c>
@@ -7479,10 +7493,10 @@
         <v>395</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28.8">
       <c r="A13" s="2" t="s">
         <v>558</v>
       </c>
@@ -7508,10 +7522,10 @@
         <v>395</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="28.8">
       <c r="A14" s="2" t="s">
         <v>560</v>
       </c>
@@ -7537,7 +7551,7 @@
         <v>395</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -7563,7 +7577,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -7575,7 +7589,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7583,7 +7597,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -7591,7 +7605,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -7599,7 +7613,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -7607,7 +7621,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -7615,7 +7629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -7644,7 +7658,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>562</v>
       </c>
@@ -7670,10 +7684,10 @@
         <v>564</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>565</v>
       </c>
@@ -7699,10 +7713,10 @@
         <v>564</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>567</v>
       </c>
@@ -7728,10 +7742,10 @@
         <v>395</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>569</v>
       </c>
@@ -7757,10 +7771,10 @@
         <v>564</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>571</v>
       </c>
@@ -7786,10 +7800,10 @@
         <v>395</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>573</v>
       </c>
@@ -7815,10 +7829,10 @@
         <v>395</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>575</v>
       </c>
@@ -7844,10 +7858,10 @@
         <v>395</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>309</v>
       </c>
@@ -7873,10 +7887,10 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>577</v>
       </c>
@@ -7902,10 +7916,10 @@
         <v>395</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>579</v>
       </c>
@@ -7931,10 +7945,10 @@
         <v>395</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>581</v>
       </c>
@@ -7960,10 +7974,10 @@
         <v>395</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>583</v>
       </c>
@@ -7989,10 +8003,10 @@
         <v>395</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.8">
       <c r="A20" s="2" t="s">
         <v>314</v>
       </c>
@@ -8018,10 +8032,10 @@
         <v>87</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
         <v>317</v>
       </c>
@@ -8047,7 +8061,7 @@
         <v>87</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -8072,8 +8086,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -8083,7 +8097,7 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -8103,7 +8117,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="32">
+    <row r="2" spans="1:9" ht="28.8">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -8123,7 +8137,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="32">
+    <row r="3" spans="1:9" ht="28.8">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -8143,7 +8157,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -8163,7 +8177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16">
+    <row r="5" spans="1:9" ht="28.8">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -8183,7 +8197,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16">
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -8203,7 +8217,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16">
+    <row r="7" spans="1:9" ht="28.8">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -8223,7 +8237,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -8242,8 +8256,11 @@
       <c r="F8" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="16">
+      <c r="I8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.8">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -8261,6 +8278,9 @@
       </c>
       <c r="F9" s="3" t="s">
         <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -8285,8 +8305,8 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -8294,7 +8314,7 @@
     <col min="4" max="4" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>585</v>
       </c>
@@ -8305,7 +8325,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -8319,7 +8339,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -8333,7 +8353,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -8347,7 +8367,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -8361,7 +8381,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16">
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -8375,7 +8395,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -8389,7 +8409,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -8402,8 +8422,11 @@
       <c r="D8" s="2" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="16">
+      <c r="I8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -8416,8 +8439,11 @@
       <c r="D9" s="2" t="s">
         <v>610</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="16">
+      <c r="I9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -8430,8 +8456,11 @@
       <c r="D10" s="2" t="s">
         <v>613</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="16">
+      <c r="I10" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -8444,8 +8473,11 @@
       <c r="D11" s="2" t="s">
         <v>616</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="16">
+      <c r="I11" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.8">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -8458,8 +8490,11 @@
       <c r="D12" s="2" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="16">
+      <c r="I12" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -8471,6 +8506,9 @@
       </c>
       <c r="D13" s="2" t="s">
         <v>622</v>
+      </c>
+      <c r="I13" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -8482,8 +8520,8 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -8491,7 +8529,7 @@
     <col min="4" max="4" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -8505,7 +8543,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -8519,7 +8557,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16">
+    <row r="3" spans="1:9" ht="28.8">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -8533,7 +8571,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -8547,7 +8585,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -8561,7 +8599,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16">
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -8575,7 +8613,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -8589,7 +8627,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -8602,8 +8640,11 @@
       <c r="D8" s="2" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="16">
+      <c r="I8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -8616,8 +8657,11 @@
       <c r="D9" s="2" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="16">
+      <c r="I9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -8630,8 +8674,11 @@
       <c r="D10" s="2" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="16">
+      <c r="I10" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -8644,8 +8691,11 @@
       <c r="D11" s="2" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="16">
+      <c r="I11" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -8658,8 +8708,11 @@
       <c r="D12" s="2" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="16">
+      <c r="I12" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -8672,8 +8725,11 @@
       <c r="D13" s="2" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="16">
+      <c r="I13" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -8686,8 +8742,11 @@
       <c r="D14" s="2" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="16">
+      <c r="I14" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -8700,8 +8759,11 @@
       <c r="D15" s="2" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="16">
+      <c r="I15" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -8713,6 +8775,9 @@
       </c>
       <c r="D16" s="2" t="s">
         <v>670</v>
+      </c>
+      <c r="I16" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -8724,8 +8789,8 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -8735,7 +8800,7 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
@@ -8755,7 +8820,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>319</v>
       </c>
@@ -8775,7 +8840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>672</v>
       </c>
@@ -8795,7 +8860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>676</v>
       </c>
@@ -8815,7 +8880,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>680</v>
       </c>
@@ -8835,7 +8900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16">
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>324</v>
       </c>
@@ -8855,7 +8920,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>327</v>
       </c>
@@ -8875,7 +8940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>686</v>
       </c>
@@ -8893,6 +8958,9 @@
       </c>
       <c r="F8" s="3" t="s">
         <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -8917,8 +8985,8 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -8928,7 +8996,7 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
@@ -8948,7 +9016,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>330</v>
       </c>
@@ -8968,7 +9036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>334</v>
       </c>
@@ -8988,7 +9056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>337</v>
       </c>
@@ -9008,7 +9076,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>692</v>
       </c>
@@ -9028,7 +9096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16">
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>696</v>
       </c>
@@ -9048,7 +9116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>340</v>
       </c>
@@ -9068,7 +9136,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>343</v>
       </c>
@@ -9087,8 +9155,11 @@
       <c r="F8" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="16">
+      <c r="I8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>346</v>
       </c>
@@ -9106,6 +9177,9 @@
       </c>
       <c r="F9" s="3" t="s">
         <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -9130,15 +9204,15 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -9149,7 +9223,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -9160,7 +9234,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -9171,7 +9245,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -9182,7 +9256,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -9193,7 +9267,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16">
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -9204,7 +9278,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -9215,7 +9289,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -9225,8 +9299,11 @@
       <c r="C8" s="2" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="16">
+      <c r="I8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -9236,8 +9313,11 @@
       <c r="C9" s="2" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="16">
+      <c r="I9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -9247,8 +9327,11 @@
       <c r="C10" s="2" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="16">
+      <c r="I10" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -9257,6 +9340,9 @@
       </c>
       <c r="C11" s="2" t="s">
         <v>722</v>
+      </c>
+      <c r="I11" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -9269,7 +9355,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -9281,7 +9367,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9289,7 +9375,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -9297,7 +9383,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -9305,7 +9391,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -9313,7 +9399,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -9321,7 +9407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -9350,7 +9436,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>349</v>
       </c>
@@ -9376,10 +9462,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>353</v>
       </c>
@@ -9405,10 +9491,10 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>355</v>
       </c>
@@ -9434,10 +9520,10 @@
         <v>87</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>357</v>
       </c>
@@ -9463,10 +9549,10 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>359</v>
       </c>
@@ -9492,10 +9578,10 @@
         <v>87</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>361</v>
       </c>
@@ -9521,10 +9607,10 @@
         <v>87</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>363</v>
       </c>
@@ -9550,10 +9636,10 @@
         <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>365</v>
       </c>
@@ -9579,7 +9665,7 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -9605,7 +9691,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -9617,7 +9703,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9625,7 +9711,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -9633,7 +9719,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -9641,7 +9727,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -9649,7 +9735,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -9657,7 +9743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -9686,7 +9772,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18">
+    <row r="8" spans="1:9" ht="17.399999999999999">
       <c r="A8" s="2" t="s">
         <v>367</v>
       </c>
@@ -9712,10 +9798,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>371</v>
       </c>
@@ -9741,10 +9827,10 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>373</v>
       </c>
@@ -9770,10 +9856,10 @@
         <v>87</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>375</v>
       </c>
@@ -9799,10 +9885,10 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.8">
       <c r="A12" s="2" t="s">
         <v>377</v>
       </c>
@@ -9828,10 +9914,10 @@
         <v>87</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>379</v>
       </c>
@@ -9857,10 +9943,10 @@
         <v>87</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>381</v>
       </c>
@@ -9886,10 +9972,10 @@
         <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>383</v>
       </c>
@@ -9915,10 +10001,10 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="18">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="17.399999999999999">
       <c r="A16" s="2" t="s">
         <v>375</v>
       </c>
@@ -9944,7 +10030,7 @@
         <v>87</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -9972,19 +10058,20 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -9992,7 +10079,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>53</v>
       </c>
@@ -10000,7 +10087,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>55</v>
       </c>
@@ -10008,7 +10095,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>57</v>
       </c>
@@ -10016,7 +10103,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>59</v>
       </c>
@@ -10024,7 +10111,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16">
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>61</v>
       </c>
@@ -10032,7 +10119,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>63</v>
       </c>
@@ -10040,44 +10127,59 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="16">
+      <c r="I8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="16">
+      <c r="I9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="16">
+      <c r="I10" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="16">
+      <c r="I11" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>74</v>
+      </c>
+      <c r="I12" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -10090,7 +10192,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I120"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -10102,7 +10204,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -10131,7 +10233,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -10157,10 +10259,10 @@
         <v>87</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -10186,10 +10288,10 @@
         <v>87</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -10215,10 +10317,10 @@
         <v>87</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -10244,10 +10346,10 @@
         <v>87</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -10273,10 +10375,10 @@
         <v>87</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -10302,10 +10404,10 @@
         <v>87</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -10331,10 +10433,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -10360,10 +10462,10 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -10389,10 +10491,10 @@
         <v>87</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -10418,10 +10520,10 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -10447,10 +10549,10 @@
         <v>87</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -10476,10 +10578,10 @@
         <v>87</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -10505,10 +10607,10 @@
         <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -10534,10 +10636,10 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -10563,10 +10665,10 @@
         <v>87</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -10592,10 +10694,10 @@
         <v>87</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -10621,10 +10723,10 @@
         <v>87</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -10650,10 +10752,10 @@
         <v>87</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -10679,10 +10781,10 @@
         <v>87</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -10708,10 +10810,10 @@
         <v>87</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -10737,10 +10839,10 @@
         <v>87</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -10766,10 +10868,10 @@
         <v>87</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -10795,10 +10897,10 @@
         <v>87</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -10824,10 +10926,10 @@
         <v>87</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -10853,10 +10955,10 @@
         <v>87</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.8">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -10882,10 +10984,10 @@
         <v>87</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -10911,10 +11013,10 @@
         <v>87</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -10940,10 +11042,10 @@
         <v>87</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -10969,10 +11071,10 @@
         <v>87</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -10998,10 +11100,10 @@
         <v>87</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -11027,10 +11129,10 @@
         <v>87</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -11056,10 +11158,10 @@
         <v>87</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -11085,10 +11187,10 @@
         <v>87</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="28.8">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -11114,10 +11216,10 @@
         <v>87</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -11143,10 +11245,10 @@
         <v>87</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -11172,10 +11274,10 @@
         <v>87</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -11201,10 +11303,10 @@
         <v>87</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -11230,10 +11332,10 @@
         <v>87</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -11259,10 +11361,10 @@
         <v>87</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -11288,10 +11390,10 @@
         <v>87</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -11317,10 +11419,10 @@
         <v>87</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -11346,10 +11448,10 @@
         <v>87</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -11375,10 +11477,10 @@
         <v>87</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -11404,10 +11506,10 @@
         <v>87</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="28.8">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -11433,10 +11535,10 @@
         <v>87</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="28.8">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -11462,10 +11564,10 @@
         <v>87</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -11491,10 +11593,10 @@
         <v>87</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -11520,10 +11622,10 @@
         <v>87</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -11549,10 +11651,10 @@
         <v>87</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -11578,10 +11680,10 @@
         <v>87</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -11607,10 +11709,10 @@
         <v>87</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -11636,10 +11738,10 @@
         <v>87</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -11665,10 +11767,10 @@
         <v>87</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -11694,10 +11796,10 @@
         <v>87</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -11723,10 +11825,10 @@
         <v>87</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -11752,10 +11854,10 @@
         <v>87</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -11781,10 +11883,10 @@
         <v>87</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="28.8">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -11810,10 +11912,10 @@
         <v>87</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="28.8">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -11839,10 +11941,10 @@
         <v>87</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -11868,10 +11970,10 @@
         <v>87</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -11897,10 +11999,10 @@
         <v>87</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -11926,10 +12028,10 @@
         <v>87</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -11955,10 +12057,10 @@
         <v>87</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -11984,10 +12086,10 @@
         <v>87</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -12013,10 +12115,10 @@
         <v>87</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -12042,10 +12144,10 @@
         <v>87</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -12071,10 +12173,10 @@
         <v>87</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -12100,10 +12202,10 @@
         <v>87</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -12129,10 +12231,10 @@
         <v>87</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -12158,10 +12260,10 @@
         <v>87</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -12187,10 +12289,10 @@
         <v>87</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -12216,10 +12318,10 @@
         <v>87</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -12245,10 +12347,10 @@
         <v>87</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="28.8">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -12274,10 +12376,10 @@
         <v>87</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="28.8">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -12303,10 +12405,10 @@
         <v>87</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="28.8">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -12332,10 +12434,10 @@
         <v>87</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="28.8">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -12361,10 +12463,10 @@
         <v>87</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="28.8">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -12390,10 +12492,10 @@
         <v>87</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="28.8">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -12419,10 +12521,10 @@
         <v>87</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="28.8">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -12448,10 +12550,10 @@
         <v>87</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="28.8">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -12477,10 +12579,10 @@
         <v>87</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="28.8">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -12506,10 +12608,10 @@
         <v>87</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="28.8">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -12535,10 +12637,10 @@
         <v>87</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="28.8">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -12564,10 +12666,10 @@
         <v>87</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="28.8">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -12593,10 +12695,10 @@
         <v>87</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="28.8">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -12622,10 +12724,10 @@
         <v>87</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="28.8">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -12651,10 +12753,10 @@
         <v>87</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="28.8">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -12680,10 +12782,10 @@
         <v>87</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="28.8">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -12709,10 +12811,10 @@
         <v>87</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="28.8">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -12738,10 +12840,10 @@
         <v>87</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="28.8">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -12767,10 +12869,10 @@
         <v>87</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="28.8">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -12796,10 +12898,10 @@
         <v>87</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="28.8">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -12825,10 +12927,10 @@
         <v>87</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="28.8">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -12854,10 +12956,10 @@
         <v>87</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="28.8">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -12883,10 +12985,10 @@
         <v>87</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="28.8">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -12912,10 +13014,10 @@
         <v>87</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -12941,10 +13043,10 @@
         <v>87</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -12970,10 +13072,10 @@
         <v>87</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -12999,10 +13101,10 @@
         <v>87</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -13028,10 +13130,10 @@
         <v>87</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -13057,10 +13159,10 @@
         <v>87</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -13086,10 +13188,10 @@
         <v>87</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -13115,10 +13217,10 @@
         <v>87</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -13144,10 +13246,10 @@
         <v>87</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -13173,10 +13275,10 @@
         <v>87</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -13202,10 +13304,10 @@
         <v>87</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -13231,10 +13333,10 @@
         <v>87</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -13260,10 +13362,10 @@
         <v>87</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -13289,10 +13391,10 @@
         <v>87</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -13318,10 +13420,10 @@
         <v>87</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -13347,10 +13449,10 @@
         <v>87</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -13376,10 +13478,10 @@
         <v>87</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -13405,10 +13507,10 @@
         <v>87</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -13434,10 +13536,10 @@
         <v>87</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -13463,10 +13565,10 @@
         <v>87</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -13492,10 +13594,10 @@
         <v>87</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -13521,10 +13623,10 @@
         <v>87</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -13550,10 +13652,10 @@
         <v>87</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -13579,7 +13681,7 @@
         <v>87</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -13604,8 +13706,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="28" customWidth="1"/>
@@ -13613,7 +13715,7 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -13630,7 +13732,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -13647,7 +13749,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -13664,7 +13766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -13681,7 +13783,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -13698,7 +13800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16">
+    <row r="6" spans="1:9">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -13715,7 +13817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -13732,7 +13834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -13748,8 +13850,11 @@
       <c r="E8" s="3">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="16">
+      <c r="I8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -13765,8 +13870,11 @@
       <c r="E9" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="16">
+      <c r="I9" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -13782,8 +13890,11 @@
       <c r="E10" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="16">
+      <c r="I10" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -13799,8 +13910,11 @@
       <c r="E11" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="16">
+      <c r="I11" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -13816,8 +13930,11 @@
       <c r="E12" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="16">
+      <c r="I12" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -13833,8 +13950,11 @@
       <c r="E13" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="16">
+      <c r="I13" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -13850,8 +13970,11 @@
       <c r="E14" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="16">
+      <c r="I14" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -13867,8 +13990,11 @@
       <c r="E15" s="3">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="16">
+      <c r="I15" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -13884,8 +14010,11 @@
       <c r="E16" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="16">
+      <c r="I16" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -13900,6 +14029,9 @@
       </c>
       <c r="E17" s="3">
         <v>8</v>
+      </c>
+      <c r="I17" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -13912,7 +14044,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -13924,7 +14056,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13932,7 +14064,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -13940,7 +14072,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -13948,7 +14080,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -13956,7 +14088,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -13964,7 +14096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -13993,7 +14125,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>393</v>
       </c>
@@ -14019,10 +14151,10 @@
         <v>395</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>396</v>
       </c>
@@ -14048,10 +14180,10 @@
         <v>395</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>398</v>
       </c>
@@ -14077,10 +14209,10 @@
         <v>395</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>400</v>
       </c>
@@ -14106,10 +14238,10 @@
         <v>395</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>402</v>
       </c>
@@ -14135,10 +14267,10 @@
         <v>395</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>404</v>
       </c>
@@ -14164,10 +14296,10 @@
         <v>395</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>83</v>
       </c>
@@ -14193,10 +14325,10 @@
         <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>88</v>
       </c>
@@ -14222,10 +14354,10 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>90</v>
       </c>
@@ -14251,10 +14383,10 @@
         <v>87</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>407</v>
       </c>
@@ -14280,10 +14412,10 @@
         <v>395</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>93</v>
       </c>
@@ -14309,10 +14441,10 @@
         <v>87</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>409</v>
       </c>
@@ -14338,7 +14470,7 @@
         <v>395</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -14364,7 +14496,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -14376,7 +14508,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14384,7 +14516,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -14392,7 +14524,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -14400,7 +14532,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -14408,7 +14540,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -14416,7 +14548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -14445,7 +14577,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>411</v>
       </c>
@@ -14471,10 +14603,10 @@
         <v>395</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>413</v>
       </c>
@@ -14500,7 +14632,7 @@
         <v>395</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -14514,7 +14646,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:9" ht="16">
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>95</v>
       </c>
@@ -14540,7 +14672,7 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -14566,7 +14698,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -14578,7 +14710,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14586,7 +14718,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -14594,7 +14726,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -14602,7 +14734,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -14610,7 +14742,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -14618,7 +14750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -14647,7 +14779,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>101</v>
       </c>
@@ -14673,10 +14805,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>106</v>
       </c>
@@ -14702,10 +14834,10 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>108</v>
       </c>
@@ -14731,10 +14863,10 @@
         <v>87</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>110</v>
       </c>
@@ -14760,10 +14892,10 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>112</v>
       </c>
@@ -14789,10 +14921,10 @@
         <v>87</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>114</v>
       </c>
@@ -14818,10 +14950,10 @@
         <v>87</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>116</v>
       </c>
@@ -14847,10 +14979,10 @@
         <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>416</v>
       </c>
@@ -14876,10 +15008,10 @@
         <v>395</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>418</v>
       </c>
@@ -14905,10 +15037,10 @@
         <v>395</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
@@ -14934,10 +15066,10 @@
         <v>87</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
         <v>120</v>
       </c>
@@ -14963,10 +15095,10 @@
         <v>87</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
         <v>420</v>
       </c>
@@ -14992,10 +15124,10 @@
         <v>395</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
         <v>422</v>
       </c>
@@ -15021,10 +15153,10 @@
         <v>395</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
         <v>424</v>
       </c>
@@ -15050,10 +15182,10 @@
         <v>395</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="2" t="s">
         <v>426</v>
       </c>
@@ -15079,10 +15211,10 @@
         <v>395</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="2" t="s">
         <v>428</v>
       </c>
@@ -15108,10 +15240,10 @@
         <v>395</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
         <v>430</v>
       </c>
@@ -15137,10 +15269,10 @@
         <v>395</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
         <v>122</v>
       </c>
@@ -15166,10 +15298,10 @@
         <v>87</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="2" t="s">
         <v>125</v>
       </c>
@@ -15195,10 +15327,10 @@
         <v>87</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
         <v>127</v>
       </c>
@@ -15224,10 +15356,10 @@
         <v>87</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
         <v>129</v>
       </c>
@@ -15253,10 +15385,10 @@
         <v>87</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
         <v>432</v>
       </c>
@@ -15282,10 +15414,10 @@
         <v>395</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="2" t="s">
         <v>131</v>
       </c>
@@ -15311,10 +15443,10 @@
         <v>87</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
         <v>434</v>
       </c>
@@ -15340,10 +15472,10 @@
         <v>395</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
         <v>436</v>
       </c>
@@ -15369,10 +15501,10 @@
         <v>395</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
         <v>438</v>
       </c>
@@ -15398,10 +15530,10 @@
         <v>395</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
         <v>134</v>
       </c>
@@ -15427,10 +15559,10 @@
         <v>87</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
         <v>137</v>
       </c>
@@ -15456,10 +15588,10 @@
         <v>87</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
         <v>140</v>
       </c>
@@ -15485,10 +15617,10 @@
         <v>87</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
         <v>142</v>
       </c>
@@ -15514,10 +15646,10 @@
         <v>87</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
         <v>144</v>
       </c>
@@ -15543,10 +15675,10 @@
         <v>87</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="2" t="s">
         <v>146</v>
       </c>
@@ -15572,10 +15704,10 @@
         <v>87</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="28.8">
       <c r="A40" s="2" t="s">
         <v>148</v>
       </c>
@@ -15601,7 +15733,7 @@
         <v>87</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
@@ -15627,7 +15759,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -15639,7 +15771,7 @@
     <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15647,7 +15779,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>76</v>
       </c>
@@ -15655,7 +15787,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>77</v>
       </c>
@@ -15663,7 +15795,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>385</v>
       </c>
@@ -15671,7 +15803,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -15679,7 +15811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -15708,7 +15840,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>151</v>
       </c>
@@ -15734,10 +15866,10 @@
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>155</v>
       </c>
@@ -15763,10 +15895,10 @@
         <v>87</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>157</v>
       </c>
@@ -15792,10 +15924,10 @@
         <v>87</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>160</v>
       </c>
@@ -15821,10 +15953,10 @@
         <v>87</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>163</v>
       </c>
@@ -15850,10 +15982,10 @@
         <v>87</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>165</v>
       </c>
@@ -15879,10 +16011,10 @@
         <v>87</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>167</v>
       </c>
@@ -15908,10 +16040,10 @@
         <v>87</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="32">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="28.8">
       <c r="A15" s="2" t="s">
         <v>170</v>
       </c>
@@ -15937,10 +16069,10 @@
         <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>173</v>
       </c>
@@ -15966,10 +16098,10 @@
         <v>87</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
         <v>175</v>
       </c>
@@ -15995,7 +16127,7 @@
         <v>87</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
